--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
+++ b/314e-ig/output/ValueSet-microorganism-by-method-vs.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
